--- a/analysis/coding.xlsx
+++ b/analysis/coding.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coding Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Ratings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Notes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Coding Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Domain Ratings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Source Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Codebook" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Adler-Milstein et al. [1]</t>
+          <t>Holmgren et al. [1]</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Holmes et al. [2]</t>
+          <t>Eden et al. [2]</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Bitar et al. [6]</t>
+          <t>Torab-Miandoab et al. [6]</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -1457,7 +1457,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Adler-Milstein et al. [1]</t>
+          <t>Holmgren et al. [1]</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr"/>
@@ -1483,7 +1483,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Holmes et al. [2]</t>
+          <t>Eden et al. [2]</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bitar et al. [6]</t>
+          <t>Torab-Miandoab et al. [6]</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr"/>
@@ -1947,6 +1947,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1977,7 +1978,7 @@
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Adler-Milstein et al. [1]</t>
+          <t>Holmgren et al. [1]</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -2004,7 +2005,7 @@
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Holmes et al. [2]</t>
+          <t>Eden et al. [2]</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2112,7 +2113,7 @@
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bitar et al. [6]</t>
+          <t>Torab-Miandoab et al. [6]</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2464,6 +2465,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
